--- a/marketing_report/outputs/Posgrados/Google_Ads_Deep_Dive/reporte_especifico_googleads.xlsx
+++ b/marketing_report/outputs/Posgrados/Google_Ads_Deep_Dive/reporte_especifico_googleads.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,7 +479,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>14909096324</t>
+          <t>14875022827</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -498,7 +498,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>15042792606</t>
+          <t>14893252513</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -517,7 +517,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>15360035696</t>
+          <t>14909096324</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -536,7 +536,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>15767139553</t>
+          <t>15042792606</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -555,19 +555,76 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>15360035696</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>15767139553</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>21676468921</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>21772187688</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
         <v>100</v>
       </c>
     </row>
@@ -619,13 +676,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
         <v>100</v>
@@ -642,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -694,7 +751,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>estudiar comercio internacional</t>
+          <t>carreras cortas</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -713,7 +770,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>relaciones internacionales carrera</t>
+          <t>estudiar comercio internacional</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -732,7 +789,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ucasal</t>
+          <t>estudiar corredor inmobiliario</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -751,7 +808,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>universidad catolica de salta</t>
+          <t>relaciones internacionales carrera</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -770,19 +827,57 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>ucasal</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>universidad catolica de salta</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>universidad de criminologia</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
         <v>100</v>
       </c>
     </row>

--- a/marketing_report/outputs/Posgrados/Google_Ads_Deep_Dive/reporte_especifico_googleads.xlsx
+++ b/marketing_report/outputs/Posgrados/Google_Ads_Deep_Dive/reporte_especifico_googleads.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
   <si>
     <t>UtmCampaign</t>
   </si>
@@ -58,6 +58,9 @@
   </si>
   <si>
     <t>21772187688</t>
+  </si>
+  <si>
+    <t>23220287690</t>
   </si>
   <si>
     <t>UtmMedium</t>
@@ -448,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -618,6 +621,23 @@
         <v>1</v>
       </c>
       <c r="E10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
         <v>100</v>
       </c>
     </row>
@@ -633,7 +653,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -650,16 +670,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2">
         <v>100</v>
@@ -677,7 +697,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -694,7 +714,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -711,7 +731,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -728,7 +748,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -745,7 +765,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -762,7 +782,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -779,7 +799,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -796,7 +816,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -813,7 +833,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9">
         <v>1</v>

--- a/marketing_report/outputs/Posgrados/Google_Ads_Deep_Dive/reporte_especifico_googleads.xlsx
+++ b/marketing_report/outputs/Posgrados/Google_Ads_Deep_Dive/reporte_especifico_googleads.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
   <si>
     <t>UtmCampaign</t>
   </si>
@@ -33,12 +33,12 @@
     <t>Tasa_%</t>
   </si>
   <si>
+    <t>14875022827</t>
+  </si>
+  <si>
     <t>14876203835</t>
   </si>
   <si>
-    <t>14875022827</t>
-  </si>
-  <si>
     <t>14893252513</t>
   </si>
   <si>
@@ -54,9 +54,6 @@
     <t>15767139553</t>
   </si>
   <si>
-    <t>21676468921</t>
-  </si>
-  <si>
     <t>21772187688</t>
   </si>
   <si>
@@ -85,9 +82,6 @@
   </si>
   <si>
     <t>relaciones internacionales carrera</t>
-  </si>
-  <si>
-    <t>ucasal</t>
   </si>
   <si>
     <t>universidad catolica de salta</t>
@@ -451,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -476,13 +470,13 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>100</v>
@@ -621,23 +615,6 @@
         <v>1</v>
       </c>
       <c r="E10">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
         <v>100</v>
       </c>
     </row>
@@ -653,7 +630,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -670,16 +647,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2">
         <v>100</v>
@@ -692,12 +669,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -714,7 +691,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -731,7 +708,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -748,7 +725,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -765,7 +742,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -782,7 +759,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -799,7 +776,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -816,7 +793,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -828,23 +805,6 @@
         <v>1</v>
       </c>
       <c r="E8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
         <v>100</v>
       </c>
     </row>
